--- a/Invoice_Tracker_Template.xlsx
+++ b/Invoice_Tracker_Template.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Stores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Equipment Types" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trends" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Invoices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stores" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Equipment Types" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Trends" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="StoreList">Stores!$A$2:$A$500</definedName>
@@ -59,7 +60,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,6 +115,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -277,7 +286,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Open Tasks by Equipment Type</a:t>
+              <a:t>Invoice Cost by Store ($)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -285,14 +294,14 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
+        <barDir val="col"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Trends'!F5</f>
+              <f>'Trends'!C5</f>
             </strRef>
           </tx>
           <spPr>
@@ -302,12 +311,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Trends'!$E$6:$E$12</f>
+              <f>'Trends'!$A$6:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$F$6:$F$12</f>
+              <f>'Trends'!$C$6:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -356,7 +365,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Cost by Month ($) — fills in as invoices arrive</a:t>
+              <a:t>Invoice Cost by Month ($)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -429,11 +438,90 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Open Tasks by Equipment</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Trends'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Trends'!$E$6:$E$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Trends'!$F$6:$F$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -455,12 +543,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="3240000"/>
+    <ext cx="4320000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -477,7 +565,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>15</col>
+      <col>16</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -492,6 +580,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -527,7 +637,28 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblStores" displayName="tblStores" ref="A1:C6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblInvoices" displayName="tblInvoices" ref="A1:L2" headerRowCount="1">
+  <autoFilter ref="A1:L2"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Invoice Date"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Store"/>
+    <tableColumn id="4" name="Equipment Type"/>
+    <tableColumn id="5" name="Cost ($)"/>
+    <tableColumn id="6" name="Vendor"/>
+    <tableColumn id="7" name="Invoice #"/>
+    <tableColumn id="8" name="Description"/>
+    <tableColumn id="9" name="Status"/>
+    <tableColumn id="10" name="Source (email)"/>
+    <tableColumn id="11" name="Date Captured"/>
+    <tableColumn id="12" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblStores" displayName="tblStores" ref="A1:C6" headerRowCount="1">
   <autoFilter ref="A1:C6"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Store"/>
@@ -538,9 +669,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblEquip" displayName="tblEquip" ref="A1:B24" headerRowCount="1">
-  <autoFilter ref="A1:B24"/>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblEquip" displayName="tblEquip" ref="A1:B25" headerRowCount="1">
+  <autoFilter ref="A1:B25"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Equipment Type"/>
     <tableColumn id="2" name="Class"/>
@@ -838,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B18"/>
+  <dimension ref="B1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -855,7 +986,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Built from your Owl Ops export. Columns now match your real data.</t>
+          <t>Two sources, one tracker. Your Owl Ops tasks + your Outlook invoices.</t>
         </is>
       </c>
     </row>
@@ -872,28 +1003,28 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>• Tasks      → your work orders / invoices. Your 9 tasks are already loaded.</t>
+          <t>• Tasks     → from Owl Ops (what broke, where). Your 9 tasks are loaded.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>• Stores     → your locations (auto-filled from the export).</t>
+          <t>• Invoices  → from Outlook. THE ROBOT FILLS THIS automatically once set up.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>• Equipment Types → the drop-down list for the Equipment column.</t>
+          <t>• Stores / Equipment Types → drop-down lists.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>• Trends     → charts: tasks by store, by equipment, and cost (fills in as invoices arrive).</t>
+          <t>• Trends    → charts. Task counts now; cost charts fill as invoices arrive.</t>
         </is>
       </c>
     </row>
@@ -903,55 +1034,21 @@
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>HOW TO ADD MORE</t>
+          <t>THE INVOICE ROBOT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>• Each new Owl Ops export: send it to me and I'll drop it straight into the Tasks tab,</t>
+          <t>Set it up once (see the setup guide I sent). After that: an invoice hits Outlook →</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  or add rows yourself — Store, Equipment, Priority, Type, Status are drop-downs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>ABOUT COST</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>These are OPEN tasks, so Cost is $0 until a vendor invoices the work. When you get an</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>invoice, type the amount in the Cost column and the Trends cost charts update automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>The Equipment Type column is my best guess from each description — please review &amp; fix.</t>
+          <t>a row appears on the Invoices tab by itself. You just glance weekly to set Equipment Type.</t>
         </is>
       </c>
     </row>
@@ -1720,117 +1817,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Address</t>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Equipment Type</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Cost ($)</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Invoice #</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Source (email)</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>Date Captured</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DD National City</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2139 E. Plaza Blvd, National City, California</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DD JJ Convoy</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4140 Convoy St, San Diego, CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DD JJ Montezuma</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5825 Montezuma Rd,  San Diego, CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DD Washington St</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>409 Washington St, San Diego, CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DD Miramar Flightline</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>8635 Obregon Ave., Bldg 8675, MCAS Miramar, San Diego, California</t>
-        </is>
-      </c>
+      <c r="A2" s="6" t="n"/>
+      <c r="B2">
+        <f>IF($A2="","",TEXT($A2,"YYYY-MM"))</f>
+        <v/>
+      </c>
+      <c r="E2" s="7" t="n"/>
+      <c r="K2" s="6" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=StoreList</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=EquipList</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pending,Approved,Paid,Disputed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1844,298 +1930,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Equipment Type</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Address</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fryer</t>
+          <t>DD National City</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2139 E. Plaza Blvd, National City, California</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Range / Oven</t>
+          <t>DD JJ Convoy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4140 Convoy St, San Diego, CA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grill / Griddle</t>
+          <t>DD JJ Montezuma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5825 Montezuma Rd,  San Diego, CA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hood / Exhaust Fan</t>
+          <t>DD Washington St</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>409 Washington St, San Diego, CA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Walk-in Cooler</t>
+          <t>DD Miramar Flightline</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Refrigeration</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Reach-in Freezer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Refrigeration</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ice Machine</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Refrigeration</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Soda / Beverage Fountain</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Coffee Machine</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Blender / Prep Equipment</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prep</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toaster</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Cooking</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Dishwasher</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Warewashing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Grease Trap</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Plumbing</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Water Heater</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Plumbing</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Rooftop HVAC Unit</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mini-split AC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>POS Terminal</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>POS / IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Receipt Printer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>POS / IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Security / CCTV</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>POS / IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Lighting / Electrical</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Plumbing / Restroom</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Plumbing</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Doors / Locks</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8635 Obregon Ave., Bldg 8675, MCAS Miramar, San Diego, California</t>
         </is>
       </c>
     </row>
@@ -2153,15 +2054,337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Equipment Type</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fryer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Range / Oven</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Grill / Griddle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hood / Exhaust Fan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Walk-in Cooler</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Reach-in Freezer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ice Machine</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Soda / Beverage Fountain</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Coffee Machine</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Blender / Prep Equipment</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toaster</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Warewashing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Grease Trap</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Water Heater</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rooftop HVAC Unit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mini-split AC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>POS Terminal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>POS / IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Receipt Printer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>POS / IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Security / CCTV</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>POS / IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lighting / Electrical</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Plumbing / Restroom</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Doors / Locks</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>— set me</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2174,7 +2397,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live from the Tasks tab.</t>
+          <t>Task counts come from Owl Ops; $ comes from invoices (fills in as the robot runs).</t>
         </is>
       </c>
     </row>
@@ -2191,29 +2414,34 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t># Open Tasks</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Invoice Cost ($)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t># Tasks</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Cost ($)</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t># Tasks</t>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Invoice Cost ($)</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2456,7 @@
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$C$2:$C$5000,$A6)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$C$2:$C$5000,$A6)</f>
         <v/>
       </c>
       <c r="E6" t="inlineStr">
@@ -2240,6 +2468,10 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E6)</f>
         <v/>
       </c>
+      <c r="G6" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2252,7 +2484,7 @@
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$C$2:$C$5000,$A7)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$C$2:$C$5000,$A7)</f>
         <v/>
       </c>
       <c r="E7" t="inlineStr">
@@ -2264,6 +2496,10 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E7)</f>
         <v/>
       </c>
+      <c r="G7" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2276,7 +2512,7 @@
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$C$2:$C$5000,$A8)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$C$2:$C$5000,$A8)</f>
         <v/>
       </c>
       <c r="E8" t="inlineStr">
@@ -2288,6 +2524,10 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E8)</f>
         <v/>
       </c>
+      <c r="G8" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2300,7 +2540,7 @@
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$C$2:$C$5000,$A9)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$C$2:$C$5000,$A9)</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
@@ -2312,6 +2552,10 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E9)</f>
         <v/>
       </c>
+      <c r="G9" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2324,7 +2568,7 @@
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$C$2:$C$5000,$A10)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$C$2:$C$5000,$A10)</f>
         <v/>
       </c>
       <c r="E10" t="inlineStr">
@@ -2336,6 +2580,10 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E10)</f>
         <v/>
       </c>
+      <c r="G10" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="E11" t="inlineStr">
@@ -2347,11 +2595,15 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E11)</f>
         <v/>
       </c>
+      <c r="G11" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Cost by Month</t>
+          <t>Invoice Cost by Month</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2363,14 +2615,18 @@
         <f>COUNTIF(Tasks!$O$2:$O$5000,$E12)</f>
         <v/>
       </c>
+      <c r="G12" s="7">
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$D$2:$D$5000,$E12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Cost ($)</t>
         </is>
@@ -2383,7 +2639,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A14)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A14)</f>
         <v/>
       </c>
     </row>
@@ -2394,7 +2650,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A15)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A15)</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2661,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A16)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A16)</f>
         <v/>
       </c>
     </row>
@@ -2416,7 +2672,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A17)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A17)</f>
         <v/>
       </c>
     </row>
@@ -2427,7 +2683,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A18)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A18)</f>
         <v/>
       </c>
     </row>
@@ -2438,7 +2694,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A19)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A19)</f>
         <v/>
       </c>
     </row>
@@ -2449,7 +2705,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A20)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A20)</f>
         <v/>
       </c>
     </row>
@@ -2460,7 +2716,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A21)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A21)</f>
         <v/>
       </c>
     </row>
@@ -2471,7 +2727,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A22)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A22)</f>
         <v/>
       </c>
     </row>
@@ -2482,7 +2738,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A23)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A23)</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2749,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A24)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A24)</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2760,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUMIFS(Tasks!$I$2:$I$5000,Tasks!$P$2:$P$5000,$A25)</f>
+        <f>SUMIFS(Invoices!$E$2:$E$5000,Invoices!$B$2:$B$5000,$A25)</f>
         <v/>
       </c>
     </row>

--- a/Invoice_Tracker_Template.xlsx
+++ b/Invoice_Tracker_Template.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,28 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -104,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +141,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -969,90 +1015,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B12"/>
+  <dimension ref="B1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Equipment &amp; Repair Tracker</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Two sources, one tracker. Your Owl Ops tasks + your Outlook invoices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>THE TABS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>• Tasks     → from Owl Ops (what broke, where). Your 9 tasks are loaded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>• Invoices  → from Outlook. THE ROBOT FILLS THIS automatically once set up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>• Stores / Equipment Types → drop-down lists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>• Trends    → charts. Task counts now; cost charts fill as invoices arrive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>THE INVOICE ROBOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Set it up once (see the setup guide I sent). After that: an invoice hits Outlook →</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>a row appears on the Invoices tab by itself. You just glance weekly to set Equipment Type.</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Invoice Robot — One-Time Setup Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="B2" s="11" t="inlineStr"/>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Do this once (~30 min). After that, invoices fill the tracker automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>BEFORE YOU START</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>1.  Save tracker to OneDrive</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Open this file → File → Save As → OneDrive. The robot needs it in the cloud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>2.  Make an Outlook folder</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>In Outlook → right-click your Inbox → New Folder → name it  Invoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>3.  Make an Outlook rule</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Outlook → Settings → Rules → New rule → 'If subject contains invoice' → Move to Invoices folder → Save</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="8" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>BUILD THE ROBOT  (go to: make.powerautomate.com — sign in with your work email)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="4" customHeight="1"/>
+    <row r="11" ht="52" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Left menu → click  + Create  →  Automated cloud flow
+Flow name: Invoice to Tracker
+Search for:  When a new email arrives (V3)  → click it → Create</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>In the trigger box:
+• Folder → folder icon → choose  Invoices
+• Click  Show advanced options  →  Only with Attachments: Yes   and   Include Attachments: Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Click + → Add an action → search:  Extract information from invoices  → click it
+(If it offers an AI Builder trial → click Yes, it's free for 30 days)
+In the  Invoice file  box → click the ⚡ lightning bolt → choose  Attachments Content
+A grey 'Apply to each' box appears — that's normal, leave it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>INSIDE the grey box → click + → Add an action
+Search:  Add a row into a table  → pick the  Excel Online (Business)  one
+• Location: OneDrive for Business   • Library: OneDrive
+• File: browse to this tracker   • Table: tblInvoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Fill the column boxes — click ⚡ in each box to pick the value:
+• Invoice Date  → Invoice date
+• Cost ($)  → Invoice total (the number one, not the text one)
+• Vendor  → Vendor name
+• Invoice #  → Invoice ID
+• Store  → Service address
+• Equipment Type  → just type the word:  Review
+• Status  → just type:  Pending
+• Date Captured  → ⚡ → Expression tab → type  utcNow()  → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Click  Save  (top right corner).  Done — the robot is live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>TEST IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="14" t="inlineStr"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Forward yourself any invoice PDF so it lands in the Outlook Invoices folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Wait ~1 minute → open this file → click the Invoices tab → a new row should be there. ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>WHAT'S AUTOMATIC vs. YOUR 10 SECONDS/WEEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Robot does automatically →</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Date · Cost · Vendor · Invoice # · drops the row · charts update themselves</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>You do (~10 sec per invoice) →</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Open Invoices tab → pick Equipment Type from the dropdown in column D → confirm Store in column C</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TROUBLESHOOTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>No row appeared?</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Power Automate → My flows → click your flow → Run history → tell me what the red X says</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Invoices in email body not PDF?</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Tell me — Step 3 changes slightly. Takes 2 min to adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>AI Builder cost after trial?</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>~$40/mo for the plan. If that's a problem tell me — I have a no-cost workaround.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>OWL OPS TASKS (the other source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>For now →</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Each week: export from Owl Ops → send me the CSV → I load the new tasks in for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>To automate it →</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Look in Owl Ops Reports for a 'Schedule' or 'Email report' button. If it exists, tell me and I'll wire that up too.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B18:C18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1206,7 +1476,6 @@
           <t>Michael Rivas</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" s="7" t="n">
         <v>0</v>
       </c>
@@ -1238,7 +1507,6 @@
         <f>IF($F2="","",TEXT($F2,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1274,7 +1542,6 @@
           <t>Ivan Gonzalez</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" s="7" t="n">
         <v>0</v>
       </c>
@@ -1306,7 +1573,6 @@
         <f>IF($F3="","",TEXT($F3,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1342,7 +1608,6 @@
           <t>Junior Berumen</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" s="7" t="n">
         <v>0</v>
       </c>
@@ -1374,7 +1639,6 @@
         <f>IF($F4="","",TEXT($F4,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1410,7 +1674,6 @@
           <t>Junior Berumen</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" s="7" t="n">
         <v>0</v>
       </c>
@@ -1442,7 +1705,6 @@
         <f>IF($F5="","",TEXT($F5,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1478,7 +1740,6 @@
           <t>Junior Berumen</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" s="7" t="n">
         <v>0</v>
       </c>
@@ -1510,7 +1771,6 @@
         <f>IF($F6="","",TEXT($F6,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1546,7 +1806,6 @@
           <t>Catherine Corcoran</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" s="7" t="n">
         <v>0</v>
       </c>
@@ -1580,7 +1839,6 @@
         <f>IF($F7="","",TEXT($F7,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1616,7 +1874,6 @@
           <t>Michael Rivas</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" s="7" t="n">
         <v>0</v>
       </c>
@@ -1648,7 +1905,6 @@
         <f>IF($F8="","",TEXT($F8,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1684,7 +1940,6 @@
           <t>Jackie Gomez</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
@@ -1716,7 +1971,6 @@
         <f>IF($F9="","",TEXT($F9,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1752,7 +2006,6 @@
           <t>Ivan Gonzalez</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" s="7" t="n">
         <v>0</v>
       </c>
@@ -1784,7 +2037,6 @@
         <f>IF($F10="","",TEXT($F10,"YYYY-MM"))</f>
         <v/>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
